--- a/光伏配储项目/电价数据/2026/英利储能站.xlsx
+++ b/光伏配储项目/电价数据/2026/英利储能站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51057</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.72524</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5652699999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.52019</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45654</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.45137</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43767</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43949</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42035</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44405</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26858</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.21861</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.26129</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.0803</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06595999999999999</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05538000000000001</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.03679</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.05861</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04984</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.02127</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.00749</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.04976</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08929000000000001</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.01904</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.01066</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21471</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24228</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.22189</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.12114</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.009849999999999999</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.16677</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.00825</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.20216</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22611</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.009390000000000001</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.04288</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.12912</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.20714</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.27794</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.00444</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.24584</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.03438</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.45757</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.53825</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.51577</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.78959</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6323799999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.52001</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.53543</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.59946</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.59301</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5465</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.51068</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.50939</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6205900000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.5769</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43476</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.43726</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.348</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.62719</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.43983</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.75886</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.79273</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5449299999999999</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52634</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5152899999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.51031</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37359</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42406</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5267000000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6554</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7523200000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44253</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.17317</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.30591</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.4519</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.09476000000000001</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.04146</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.27305</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.22857</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>-0.01254</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>-0.00491</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.00445</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.00542</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.37255</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6066699999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>-0.00797</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.004929999999999999</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.00518</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.61665</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.40642</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.00756</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.00482</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>-0.00451</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.2704</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.23628</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.16547</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.24495</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.25257</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23991</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.43592</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.41636</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.27868</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.48658</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.70505</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7449600000000001</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.86705</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.43174</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.8547400000000001</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43469</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41067</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3111</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.43976</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.4922</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.29331</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.30266</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47387</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.2717</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.27342</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.25378</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.30642</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.04407</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.01274</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.03865</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.0114</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.03181</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.04104</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.03864</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.03012</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.04401</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.01094</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.02251</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.05126</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.05185</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.07490999999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.23113</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.15494</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.21272</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.19803</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.25004</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.27255</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.26032</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.25157</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.14094</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.5003299999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.02445</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39857</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3432</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.26882</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.27237</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.27242</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.2809700000000001</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.28036</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.28028</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.29896</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.29778</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29583</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.26455</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.20045</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.03071</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11653</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.09098000000000001</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.27009</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.21353</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.15013</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.44528</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.22681</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.03481</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.02503</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.1021</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.28471</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.18155</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.01674</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.23279</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.01451</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.03346</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.05352000000000001</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.08051999999999999</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.20029</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.16641</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.20271</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.14992</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19653</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.11865</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.18774</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.22664</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.27926</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.26193</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.29166</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42111</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.49913</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.29839</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.25698</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29198</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.27541</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.27373</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.27653</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21904</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.10314</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37383</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41614</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.351</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6687000000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44602</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.09831000000000001</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14031</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33587</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31995</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.16984</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22474</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.27542</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>-0.01059</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.27758</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.09762999999999999</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15669</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.19457</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.28952</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.27605</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62201</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78099</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92031</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92864</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.90703</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.32038</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.39755</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.9311</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63924</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.23001</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.89022</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.58214</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.37475</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.06312</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5747100000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8281799999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.8104199999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.8072</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8813799999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8934</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5280900000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.43282</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.44397</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.48944</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.25107</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.66588</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54887</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50997</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46076</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42905</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44453</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45155</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45275</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42196</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39667</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39115</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41331</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58761</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59596</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6017100000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6433099999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46542</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.6784199999999999</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.7821399999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.24457</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43935</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.0109</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45236</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.354</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.02146</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4999</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.49958</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.6251100000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.69601</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41854</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.45008</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.5134500000000001</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.45009</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16551</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29485</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.06148</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.28092</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.28614</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.29276</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.29862</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25559</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.24823</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42745</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.24369</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44683</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59663</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35475</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13558</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7114199999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.80536</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65058</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58951</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43711</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.02355</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.28836</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.28448</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.27824</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.28483</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.27063</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.26669</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.27839</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.27099</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2501</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.25715</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.38871</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.27133</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.2622</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.24751</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.11688</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.26669</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29345</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.47961</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.4537</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.6910700000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46542</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43832</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3248</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42373</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.03027</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.04702000000000001</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.01058</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.2425</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.15282</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.15675</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.1639</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.12841</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.19432</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14668</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14668</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.06806</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11722</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11685</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.16017</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.15248</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28495</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4498</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34932</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.45989</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46858</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.07551999999999999</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.00158</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.25044</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.25044</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.24323</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>-0.01107</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.18501</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.09987</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>-0.01125</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.15096</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>-0.01036</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>-0.01073</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.20242</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.16257</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.28801</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>-0.01087</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.20075</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.21156</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>-0.01131</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.19497</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.18329</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.01035</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>-0.01122</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.21214</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>-0.0112</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.01238</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29968</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.29659</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44087</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.46441</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.42345</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38499</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.51436</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.38891</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.28304</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.25814</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.27019</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.09759000000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.21513</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.45065</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.41241</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.51293</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7892899999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.43982</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.37123</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.52038</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41502</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30966</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>-0.01669</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29086</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>-0.01708</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28262</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34457</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>-0.03722</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.7447999999999999</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.41667</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.62473</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48484</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45231</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.345</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41172</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26533</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19865</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25538</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.03543</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.12839</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.02282</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23868</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28783</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.25003</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.00723</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.005650000000000001</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.24571</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.24397</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.71614</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6624800000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6932200000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46533</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.5982999999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48317</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.92291</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.4575</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.47846</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40622</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48276</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36002</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49261</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48125</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48125</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40593</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56031</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45022</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.41936</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41993</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.43606</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.40948</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.20066</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.004070000000000001</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.16486</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.04991</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.06295000000000001</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.00509</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.20727</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.05122</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.13346</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.04954</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.29763</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.06526</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.42467</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49048</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.51008</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.4354</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6437999999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7990700000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.6949</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.7949299999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.88967</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.6363</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.57873</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.9899600000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.9056799999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.70353</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.77025</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.4637</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.54277</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.5296799999999999</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.52046</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.5166000000000001</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.44182</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.61293</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.45131</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4700299999999999</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.49088</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4639</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.44894</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.46494</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43793</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.48689</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.41195</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.42239</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.41195</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39358</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18497</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4059700000000001</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46056</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.02511</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18386</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41195</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39311</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40896</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.38403</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.41195</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.3992</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37793</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.09537000000000001</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.07764</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.30022</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.25048</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23541</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23841</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24725</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25286</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.04224</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.15087</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.06059</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.17745</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.26005</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.04414</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.15002</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15287</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.06107</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.01478</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.12369</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.04752</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.03767</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.02623</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.15105</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.02366</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.0113</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.03746</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34996</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19113</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.1819</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.1486</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.04947</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.04438</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-0.04854</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.13777</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.19031</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27705</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.22319</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.22401</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22306</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.22821</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.23816</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.26524</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.24784</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.24103</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.23242</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.24803</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25116</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.23443</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.2526</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.24132</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.25859</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.24648</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.25999</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.2745</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.27452</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.25672</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.21608</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.23691</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.21444</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.18344</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.07947</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.04249</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.22909</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.14947</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.15094</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.15226</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.01806</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.23185</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.21269</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.19941</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16152</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15329</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.12909</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.15145</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.18609</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.10621</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.11846</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.18805</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.15553</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.20752</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.17929</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.16688</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.21691</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.16636</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.21792</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.29145</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.22559</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.20847</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.21682</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.12714</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.45391</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.20268</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.01481</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.18554</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.16631</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.00643</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.02536</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.18704</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.26553</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.07956000000000001</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.01322</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.325</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.26143</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25678</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.12366</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24658</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.43356</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.00281</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.19284</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.15062</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.11078</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.331</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.23965</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.26255</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.27869</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.03202</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.28542</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.28014</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.26994</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.27138</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.26914</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.06812</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.07423</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.45886</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.56414</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.42759</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37263</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.5672200000000001</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.49409</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.47504</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43142</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>1.06653</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.51212</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.42974</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.47768</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.41281</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.369</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47621</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.46911</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.21182</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.19752</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.27949</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.19952</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.27885</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.42764</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39648</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.43934</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41918</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49494</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5757100000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.56699</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.47664</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5650700000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49253</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5099900000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.41214</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.55388</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.53886</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.81565</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.85666</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.57096</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5716</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.4458</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39787</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3756</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27232</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.27059</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.26716</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.27901</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.26702</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.26247</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.25461</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.24876</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.2474</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.25523</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.26599</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.20174</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.22331</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.15028</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.01861</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.01898</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.01457</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.02876</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.04184</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.02892</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.0341</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.00725</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.00083</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.00327</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.04316</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.04744</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03692</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.03957</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.03902000000000001</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.12424</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.09112000000000001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.13209</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.15616</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.18722</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.23935</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.19471</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.21087</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.21738</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.25851</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37793</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40366</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40702</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.40512</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.43178</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.39485</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38017</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8191900000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37224</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.28366</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.27662</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.2541</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.24643</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.21016</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.2072</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.2216</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.21676</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>-0.00805</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.00729</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.00729</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.00729</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.08835999999999999</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>-0.02819</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.00729</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.00729</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.00729</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16025</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.009310000000000001</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.00758</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>-0.00869</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.01387</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>-0.00855</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-0.009439999999999999</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-0.01045</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.06235</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.22083</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.18018</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.21201</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.29673</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43143</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.50044</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.38637</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41645</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.38319</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.38648</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.40361</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.50224</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41684</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.26984</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.23025</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.18373</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.17002</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.11078</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.14497</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.16914</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.15723</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.08173</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.10167</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.06467000000000001</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03756</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03693</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03693</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03721</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.05971</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02895</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.05293</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.06837</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.1128</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.12608</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.08506999999999999</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.16009</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.14235</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.08644</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.0461</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21461</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.09276999999999999</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.08745</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.18557</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.12644</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.14974</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.16152</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.14313</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.17677</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.19739</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.19888</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.21275</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.25778</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.25824</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.27924</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39729</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.26561</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.48136</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40438</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.43629</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.40604</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40815</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40205</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37047</v>
       </c>
     </row>
   </sheetData>
